--- a/notebook/dataset/Triage-Module-Evaluation-Checkpoint-002.xlsx
+++ b/notebook/dataset/Triage-Module-Evaluation-Checkpoint-002.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the employee was not allowed to take a 3-month leave from the employer.&gt;</t>
+          <t>&lt;I was not allowed to take a 3-month leave by my employer.&gt;</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,8 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the person wants to go home but the ticket is not being given to them.&gt;</t>
+          <t>&lt;Normalized English Text&gt;
+It is alleged that the individual wishes to return home but the ticket is not being provided.</t>
         </is>
       </c>
     </row>
@@ -576,7 +577,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the contract I signed is different from what was discussed with the agency.&gt;</t>
+          <t>&lt;I am being forced to sign a contract that is different from what was discussed with the agency.&gt;</t>
         </is>
       </c>
     </row>
@@ -600,7 +601,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the salary is being withheld for food purposes.&gt;</t>
+          <t>&lt;Is it legal for my salary to be deducted for food?&gt;</t>
         </is>
       </c>
     </row>
@@ -745,7 +746,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the individual works more than 16 hours per day, and it is questioned whether this is prohibited.&gt;</t>
+          <t>&lt;I am employed for more than 16 hours per day, which is allegedly prohibited?&gt;</t>
         </is>
       </c>
     </row>
@@ -890,7 +891,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that an employee's salary is legally allowed to be reduced if their equipment is damaged&gt;</t>
+          <t>&lt;Issues regarding salary reduction due to damaged property&gt;</t>
         </is>
       </c>
     </row>
@@ -986,7 +987,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>&lt;Brought to you by the court, they want to send me back, is that legal?&gt;</t>
+          <t>&lt;I am pregnant and they want to send me home, is that legal?&gt;</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1011,8 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that a agency fee is being charged again for renewal.&gt;</t>
+          <t>&lt;Normalized English Text&gt;
+It is alleged that an agency fee is being charged again for the renewal.</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1254,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>&lt;I am afraid to report because I might be deported&gt;</t>
+          <t>&lt;I am afraid to report because I may be deported&gt;</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1278,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>&lt;Valid pa ba ang visa ko kung na-terminate ako kahapon?&gt;</t>
+          <t>&lt;Does the visa remain valid if I was terminated yesterday?&gt;</t>
         </is>
       </c>
     </row>
@@ -1665,8 +1667,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>&lt;Normalized English Text&gt;
-It is alleged that the individual wishes to inquire about the status of their case with the NLRC.</t>
+          <t>&lt;I would like to know the status of my case at the NLRC.&gt;</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1765,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>&lt;Check whether the agency I spoke to is legitimate&gt;</t>
+          <t>&lt;Please check whether the agency I spoke to is legitimate.&gt;</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the individual has been verbally harassed by their employer and asks if a complaint can be filed.&gt;</t>
+          <t>&lt;Help, it is alleged that the employer has verbally harassed the individual, can a complaint be filed?&gt;</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1933,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>&lt;How to claim Long Service Payment if you have worked for 5 years?&gt;</t>
+          <t>&lt;P&gt;How to claim Long Service Payment if I have worked for 5 years?&lt;/P&gt;</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2077,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>&lt;I refuse to be given my plane ticket back, what are my rights?&gt;</t>
+          <t>I am not receiving my return plane ticket, what are my rights?</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2125,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that the employer stated that the employee must work on Sundays, which is not allowed?&gt;</t>
+          <t>&lt;I am alleged to have been told by my employer that I must work on Sundays, which is not allowed?&gt;</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2149,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>&lt;How to apply for an OEC online, the website is down&gt;</t>
+          <t>&lt;How to apply for an OEC online, as the website is down&gt;</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>&lt;I am physically assaulted by my employer. Where should I file a complaint?&gt;</t>
+          <t>&lt;I am physically assaulted by my employer, where should I file a complaint?&gt;</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2437,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>&lt;It is alleged that my visa was canceled without informing me. Is this legal?&gt;</t>
+          <t>&lt;They canceled my visa without informing me, is this legal?&gt;</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2461,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>&lt;I do not know what to do, I am not being given a release letter&gt;</t>
+          <t>&lt;I do not know what to do, I am not being given a release letter?&gt;</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2533,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>&lt;Ask whether the insurance covers an accident at work?&gt;</t>
+          <t>&lt;Ask whether the insurance covers an accident at work&gt;</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2557,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>&lt;Is it prohibited to use a mobile phone during working hours?&gt;</t>
+          <t>&lt;Does it really prohibit the use of mobile phones during working hours?&gt;</t>
         </is>
       </c>
     </row>
@@ -2605,8 +2606,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>&lt;Normalized English Text&gt;
-Is it legal for 24 hours of surveillance to be conducted via CCTV in my room?</t>
+          <t>&lt;It is alleged that the room is monitored by CCTV for 24 hours.&gt;</t>
         </is>
       </c>
     </row>
@@ -2871,8 +2871,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>&lt;Normalized English Text&gt;
-The employer did not pay the MPF, may the employee report this?</t>
+          <t>&lt;Did not receive MPF payment, can report?&gt;</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2914,12 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>" It is alleged that the person has worked for five years and asks whether they should be entitled to long service money. "
-&lt;Cantoneseness: Cantonese&gt;</t>
+          <t>" It is alleged that the person has worked for five years and asks whether they should be entitled to long service money. "</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3042,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>&lt;If I work a part-time job during my vacation, will it be illegal?&gt;</t>
+          <t>&lt;If I work a part-time job during my vacation, would it be illegal?&gt;</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3066,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>&lt;I am alleged to have had my passport taken by my employer and not returned.&gt;</t>
+          <t>&lt;I am alleged to have had my passport taken by my employer and not returned&gt;</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3213,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>"I am required to live in the employer's house? Can I go out and live elsewhere?"</t>
+          <t>"I am required to live at the employer's house? Can I go out and live elsewhere?"</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3262,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>&lt;I have been hit by my boss. Am I able to file a lawsuit against him?&gt;</t>
+          <t>&lt;I have been hit by my boss. Am I allowed to sue him?&gt;</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3336,7 @@
       <c r="F120" t="inlineStr">
         <is>
           <t>&lt;Normalized English Text&gt;
-The intermediary company has charged me a lot of money. Is this illegal?</t>
+It is alleged that the intermediary company has collected a large amount of money from the complainant. Is this legal?</t>
         </is>
       </c>
     </row>
@@ -3436,8 +3434,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>&lt;Normalized English Text&gt;
-What is the method for calculating mandatory provident fund contributions?</t>
+          <t>"Please inquire about how the mandatory provident fund contributions are calculated?"</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3459,7 @@
       <c r="F125" t="inlineStr">
         <is>
           <t>&lt;Normalized English Text&gt;
-The person did not provide me with the required notice period, and I am wondering what steps I can take to pursue this.</t>
+The person did not provide me with the required notice period, and I am wondering what legal actions I can take.</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3484,7 @@
       <c r="F126" t="inlineStr">
         <is>
           <t>&lt;Normalized English Text&gt;
-It is alleged that a contract was signed and the party now regrets it. Can the contract be canceled?</t>
+It is alleged that a contract was signed and the party regrets it, can it be canceled?</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3534,7 @@
       <c r="F128" t="inlineStr">
         <is>
           <t>&lt;Normalized English Text&gt;
-It is alleged that an employee is required to work 20 hours per day and is experiencing difficulty with this. Can the employee report this to the Labour Department?</t>
+It is alleged that an employee is required to work 20 hours per day and is unable to comply. Is it possible to report this to the Labour Department?</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3558,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>我未收到最後一期糧食，如何處理？</t>
+          <t>&lt;I have not received the last installment of food. How to proceed?&gt;</t>
         </is>
       </c>
     </row>
@@ -3633,8 +3630,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>&lt;Normalized English Text&gt;
-The visa was denied, when must I depart?</t>
+          <t>"Visa was denied, when must I depart?"</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3754,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>"Is the statutory holiday mandatory to be given?"</t>
+          <t>"Is the statutory holiday mandatory?"</t>
         </is>
       </c>
     </row>
@@ -4119,12 +4115,13 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>" It is alleged that the person did not want to terminate the contract, but due to financial difficulties, they cannot afford to pay one month's rent and ask if they can leave immediately. "</t>
+          <t>" It is alleged that the person performed well but did not want to terminate the contract, but the person does not have money to pay one month's salary, can they leave immediately? "
+&lt;Cantonesee: Cantonese&gt;</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4171,7 @@
       <c r="F154" t="inlineStr">
         <is>
           <t>&lt;Normalized English Text&gt;
-It is alleged that he only provides three thousand yuan or so each month, claiming that some amount has been withheld as a brokerage fee, but the individual has not signed any consent form.</t>
+It is alleged that he only provides three thousand yuan and some change every month, claiming that some amount is withheld as a brokerage fee, but the complainant has not signed any consent form.</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4190,13 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>"Contract states that food and accommodation are provided, but no meal allowance is given each month, and I am required to use my own salary to buy groceries and cook myself. Does this constitute a violation of law?"</t>
+          <t>"Contract states that food and accommodation are provided, but no meal allowance is given each month, and I am required to use my own salary to buy groceries and cook myself. Does this constitute a legal violation?"
+&lt;Cantoneseness: Cantonese&gt;</t>
         </is>
       </c>
     </row>
@@ -4265,13 +4263,12 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>&lt;I am employed from 6 AM to 1 AM daily, with no personal time for rest. Do I have the right to request fixed rest time?&gt;
-&lt;Cantonese&gt;</t>
+          <t>&lt;I am employed from 6 AM to 1 AM daily, with no personal time for rest. Do I have the right to request fixed rest time?&gt;</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4292,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>"Employer forced me to sign a 'voluntary resignation' letter, saying if I don't sign, they will report me for stealing. I am scared. What should I do?"</t>
+          <t>"Employer forced me to sign a 'voluntary resignation' letter, saying if I don't sign, they will report me for stealing. I am very scared. What should I do?"</t>
         </is>
       </c>
     </row>
@@ -4314,13 +4311,13 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Cantonese</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>"Employee worked for three months, employer stated that employee worked too slowly and terminated the contract, is the employer required to be responsible for the employee's return ticket?"
-&lt;Cantonesse: Cantonese&gt;</t>
+          <t>&lt;Normalized English Text&gt;
+It is alleged that the employer terminated the contract due to the employee's slow work performance after three months, and the employee is asking whether the employer is responsible for the cost of the return ticket.</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4386,13 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cantonese</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>" It is alleged that the employee was told that his performance last week was poor, so his salary will be reduced by 500 dollars this month as punishment. Is there any labor law that prohibits this?"</t>
+          <t>"Someone stated that I performed poorly last week, so my salary will be reduced by 500 dollars this month as punishment. Does the labor law prohibit this?"
+&lt;Cantoneseness: Cantonese&gt;</t>
         </is>
       </c>
     </row>
@@ -4485,17 +4483,8 @@
       </c>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Cantonese</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>&lt;Normalized English Text&gt;
-The caregiver alleges that the person under care has passed away, and the son stated that the contract is immediately terminated, requiring the caregiver to purchase a ticket back to the Philippines tomorrow. How should the severance pay be calculated?</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4510,16 +4499,8 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Cantonese</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>"I am alleged to have done housework and been asked by my boss to work at his restaurant to wash dishes every day. Is this considered forced labor?"</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
